--- a/WORD/4_21_12.xlsx
+++ b/WORD/4_21_12.xlsx
@@ -467,1059 +467,1055 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>情景</t>
+          <t>状況</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>じょうけい</t>
+          <t>じょうきょう</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>じょけい-&gt;叙景</t>
+          <t>同“情況”</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>時刻</t>
+          <t>たちまち</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>じこく</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>时间；时刻</t>
+          <t>转眼间；忽然</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>介護</t>
+          <t>傾向</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>かいご</t>
+          <t>けいこう</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>护理；照料；看护</t>
+          <t>趋势</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>会合</t>
+          <t>漏れる</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>かいごう</t>
+          <t>もれる</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>聚会；集会</t>
+          <t>(液体、气体)泄露；消息走漏</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>勘合</t>
+          <t>雇う</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>かんごう</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>核对；验证；对照</t>
-        </is>
-      </c>
+          <t>やとう</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>看護</t>
+          <t>栽培</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>かんご</t>
+          <t>さいばい</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>护理; 看护; 照料</t>
+          <t>种植；培养</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>焦る</t>
+          <t>命令</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>あせる</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>焦急；急躁</t>
-        </is>
-      </c>
+          <t>めいれい</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>𠮟る</t>
+          <t>反対</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>しかる</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>责骂;叱责;责备</t>
-        </is>
-      </c>
+          <t>はんたい</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>創造</t>
+          <t>任せる</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>そうぞう</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>まかせる</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>委托；托付</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>借りる</t>
+          <t>景色</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>かりる</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>借用；租赁</t>
-        </is>
-      </c>
+          <t>けしき</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ぎりぎり</t>
+          <t>否定</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>最大限度，极限，到底</t>
+          <t>ひてい</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>思い切って</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>映る</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>うつる</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>下决心；果断地</t>
+          <t>映照；反映；配合</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>うっかり</t>
+          <t>仕える</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>疏忽；不留神；无意中</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>つかえる</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>侍奉；服务</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>せっかく</t>
+          <t>最寄りの</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>特意地</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>もよりの</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>最近的；就近的</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>知らず知らず</t>
+          <t>勧める</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>不知不觉</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>すすめる</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>劝告；推荐；邀请</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>最寄りの</t>
+          <t>創造</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>もよりの</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>最近的；就近的</t>
-        </is>
-      </c>
+          <t>そうぞう</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>貧しい</t>
+          <t>ぎりぎり</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>まずしい</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>贫穷；贫困</t>
-        </is>
-      </c>
+          <t>最大限度，极限，到底</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>映る</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>うつる</t>
-        </is>
-      </c>
+          <t>せっかく</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>映照；反映；配合</t>
+          <t>特意地</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>景色</t>
+          <t>誘う</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>けしき</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>さそう</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>邀请；引诱；引起；招致</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>状況</t>
+          <t>思い切って</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>じょうきょう</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>同“情況”</t>
-        </is>
-      </c>
+          <t>下决心；果断地</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>焦げる</t>
+          <t>稼ぐ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>こげる</t>
+          <t>かせぐ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>烧焦；烤焦；烤糊</t>
+          <t>赚钱；获得（时间、名声等）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>賛成</t>
+          <t>解約</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>さんせい</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>同意；赞成</t>
-        </is>
-      </c>
+          <t>かいやく</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>久々</t>
+          <t>ばりばり</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ひさびさ</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>时隔很久；好久。</t>
-        </is>
-      </c>
+          <t>干劲十足</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>永遠</t>
+          <t>急激</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>えいえん</t>
+          <t>きゅうげき</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>永久；永恒；长久</t>
+          <t>急剧；急速(变化、事态)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>満たす</t>
+          <t>掴む</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>みたす</t>
+          <t>つかむ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>满足；填充；使充满</t>
+          <t>抓住；掌握；理解</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>詰める</t>
+          <t>外見</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>つめる</t>
+          <t>がいけん</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>塞满；填满</t>
+          <t>外表；外貌；外观</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>積もる</t>
+          <t>容姿</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>つもる</t>
+          <t>ようし</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>积累；堆积；估计；预计</t>
+          <t>容貌；姿色</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>順調</t>
+          <t>様子</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>じゅんちょう</t>
+          <t>ようす</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>顺利；顺畅；正常</t>
+          <t>情况；状态；情形</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>誘う</t>
+          <t>永遠</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>さそう</t>
+          <t>えいえん</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>邀请；引诱；引起；招致</t>
+          <t>永久；永恒；长久</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>勧める</t>
+          <t>指図</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>すすめる</t>
+          <t>さしず</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>劝告；推荐；邀请</t>
+          <t>指示；命令；吩咐</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>仕える</t>
+          <t>工作</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>つかえる</t>
+          <t>こうさく</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>侍奉；服务</t>
+          <t>制作；加工；工艺</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>任せる</t>
+          <t>形成</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>まかせる</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>委托；托付</t>
-        </is>
-      </c>
+          <t>けいせい</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>否定</t>
+          <t>レンタル</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ひてい</t>
+          <t>rental出租，出赁</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>レンタル</t>
+          <t>解消</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>rental出租，出赁</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>かいしょう</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>解除；消除；取消</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ばりばり</t>
+          <t>廃止</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>干劲十足</t>
+          <t>はいし</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>指図</t>
+          <t>焦げる</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>さしず</t>
+          <t>こげる</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>指示；命令；吩咐</t>
+          <t>烧焦；烤焦；烤糊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>雇う</t>
+          <t>介護</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>やとう</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>かいご</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>护理；照料；看护</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>掴む</t>
+          <t>順調</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>つかむ</t>
+          <t>じゅんちょう</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>抓住；掌握；理解</t>
+          <t>顺利；顺畅；正常</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>格好</t>
+          <t>満たす</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>かっこう</t>
+          <t>みたす</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>外形；装束；体面；姿态；样子</t>
+          <t>满足；填充；使充满</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>外見</t>
+          <t>勘合</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>がいけん</t>
+          <t>かんごう</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>外表；外貌；外观</t>
+          <t>核对；验证；对照</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>容姿</t>
+          <t>野党</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ようし</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>容貌；姿色</t>
-        </is>
-      </c>
+          <t>やとう</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>様子</t>
+          <t>貧しい</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ようす</t>
+          <t>まずしい</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>情况；状态；情形</t>
+          <t>贫穷；贫困</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>開設</t>
+          <t>情景</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>かいせつ</t>
+          <t>じょうけい</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>设立;开设;创办</t>
+          <t>じょけい-&gt;叙景</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>工作</t>
+          <t>詰める</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>こうさく</t>
+          <t>つめる</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>制作；加工；工艺</t>
+          <t>塞满；填满</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>形成</t>
+          <t>借りる</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>けいせい</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>かりる</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>借用；租赁</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>セールス</t>
+          <t>𠮟る</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>しかる</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>责骂;叱责;责备</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>解消</t>
+          <t>会合</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>かいしょう</t>
+          <t>かいごう</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>解除；消除；取消</t>
+          <t>聚会；集会</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中止</t>
+          <t>開設</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ちゅうし</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>かいせつ</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>设立;开设;创办</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>命令</t>
+          <t>じりじり</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>めいれい</t>
+          <t>逐渐地</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>廃止</t>
+          <t>さっさと</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>はいし</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>赶快</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>じりじり</t>
+          <t>中止</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>逐渐地</t>
+          <t>ちゅうし</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>解約</t>
+          <t>時刻</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>かいやく</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>じこく</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>时间；时刻</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>たちまち</t>
+          <t>うっかり</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>转眼间；忽然</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>疏忽；不留神；无意中</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>稼ぐ</t>
+          <t>格好</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>かせぐ</t>
+          <t>かっこう</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>赚钱；获得（时间、名声等）</t>
+          <t>外形；装束；体面；姿态；样子</t>
         </is>
       </c>
     </row>
@@ -1529,18 +1525,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>傾向</t>
+          <t>担う</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>けいこう</t>
+          <t>になう</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>承担；担负；肩负</t>
         </is>
       </c>
     </row>
@@ -1550,18 +1546,18 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>漏れる</t>
+          <t>勧誘</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>もれる</t>
+          <t>かんゆう</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(液体、气体)泄露；消息走漏</t>
+          <t>劝诱；邀请</t>
         </is>
       </c>
     </row>
@@ -1571,20 +1567,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>急激</t>
+          <t>詳しい</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>きゅうげき</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>急剧；急速(变化、事态)</t>
-        </is>
-      </c>
+          <t>くわしい</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1592,18 +1584,18 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>栽培</t>
+          <t>賛成</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>さいばい</t>
+          <t>さんせい</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>种植；培养</t>
+          <t>同意；赞成</t>
         </is>
       </c>
     </row>
@@ -1613,14 +1605,18 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>さっさと</t>
+          <t>看病</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>かんびょう</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>赶快</t>
+          <t>护理，看护</t>
         </is>
       </c>
     </row>
@@ -1630,132 +1626,132 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>反対</t>
+          <t>上映</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>はんたい</t>
+          <t>じょうえい</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>勧誘</t>
+          <t>積もる</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>かんゆう</t>
+          <t>つもる</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>劝诱；邀请</t>
+          <t>积累；堆积；估计；预计</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>永久</t>
+          <t>セールス</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>えいきゅう</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>担う</t>
+          <t>知らず知らず</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>になう</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>承担；担负；肩负</t>
-        </is>
-      </c>
+          <t>不知不觉</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>自慢</t>
+          <t>看護</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>かんご</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>自夸；吹嘘；炫耀</t>
+          <t>护理; 看护; 照料</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>注意</t>
+          <t>焦る</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ちゅうい</t>
+          <t>あせる</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>留神；当心；小心；提醒；告诫</t>
+          <t>焦急；急躁</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>賛否</t>
+          <t>久々</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>さんぴ</t>
+          <t>ひさびさ</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>赞成与否</t>
+          <t>时隔很久；好久。</t>
         </is>
       </c>
     </row>
@@ -1765,20 +1761,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>占める</t>
+          <t>ストライキ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>しめる</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>占据；占有</t>
-        </is>
-      </c>
+          <t>strike；罢工</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1786,13 +1778,13 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>エコノミー</t>
+          <t>久しい</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>economy</t>
+          <t>ひさしい</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
@@ -1803,20 +1795,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>積む</t>
+          <t>永久</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>つむ</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>积累；装载；堆积</t>
-        </is>
-      </c>
+          <t>えいきゅう</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1824,16 +1812,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>含む</t>
+          <t>自慢</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>ふくむ</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>自夸；吹嘘；炫耀</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1841,16 +1829,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>野党</t>
+          <t>注意</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>やとう</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>ちゅうい</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>留神；当心；小心；提醒；告诫</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1858,16 +1850,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>久しい</t>
+          <t>占める</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ひさしい</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>しめる</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>占据；占有</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1875,13 +1871,13 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>祈る</t>
+          <t>エコノミー</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>いのる</t>
+          <t>economy</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -1892,16 +1888,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ストライキ</t>
+          <t>積む</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>strike；罢工</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>つむ</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>积累；装载；堆积</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1930,20 +1930,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>散布</t>
+          <t>含む</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>さんぷ</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>散布；传播；散布消息</t>
-        </is>
-      </c>
+          <t>ふくむ</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1951,16 +1947,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ニーズ</t>
+          <t>散布</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>needs</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>さんぷ</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>散布；传播；散布消息</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1968,20 +1968,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>迷う</t>
+          <t>ニーズ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>まよう</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>犹豫；迷失；困惑</t>
-        </is>
-      </c>
+          <t>needs</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1989,18 +1985,18 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>乏しい</t>
+          <t>迷う</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>とぼしい</t>
+          <t>まよう</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>缺乏，不足，缺少</t>
+          <t>犹豫；迷失；困惑</t>
         </is>
       </c>
     </row>
@@ -2010,16 +2006,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>詳しい</t>
+          <t>乏しい</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>くわしい</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>とぼしい</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>缺乏，不足，缺少</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2027,18 +2027,18 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>看病</t>
+          <t>貧乏</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>かんびょう</t>
+          <t>びんぼう</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>护理，看护</t>
+          <t>贫穷；贫困</t>
         </is>
       </c>
     </row>
@@ -2048,18 +2048,18 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>貧乏</t>
+          <t>怪しい</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>びんぼう</t>
+          <t>あやしい</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>贫穷；贫困</t>
+          <t>可疑；奇异；靠不住</t>
         </is>
       </c>
     </row>
@@ -2069,20 +2069,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>怪しい</t>
+          <t>祈る</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>あやしい</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>可疑；奇异；靠不住</t>
-        </is>
-      </c>
+          <t>いのる</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2090,16 +2086,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>上映</t>
+          <t>賛否</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>じょうえい</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>さんぴ</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>赞成与否</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
